--- a/cmdList.xlsx
+++ b/cmdList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Biamine\ressourcepack\Ressourcepack-for-biamine\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bianca\Desktop\Server biamine\custom plugin\1_Resourcepacks\Github\Ressourcepack-for-biamine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E691E5C-9CAE-4A6B-8FFA-BFB3FB363838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A2DBDA-9730-4C9B-83F4-EEF8F2D4813E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Custom Models" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="166">
   <si>
     <t>Key (Legende)</t>
   </si>
@@ -509,6 +509,15 @@
   </si>
   <si>
     <t>trophy: Server B-Day</t>
+  </si>
+  <si>
+    <t>cottone candy</t>
+  </si>
+  <si>
+    <t>timbits</t>
+  </si>
+  <si>
+    <t>brezel</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J149"/>
+  <dimension ref="B2:J151"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2034,54 +2043,68 @@
         <v>50</v>
       </c>
     </row>
-    <row r="76" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B76" s="23" t="s">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B74" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="12">
+        <v>6</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E74" s="14" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B75" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="12">
+        <v>6</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E75" s="14" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B76" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" s="12">
+        <v>6</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E76" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B78" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C76" s="24"/>
-      <c r="D76" s="24"/>
-      <c r="E76" s="24"/>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B77" s="1" t="s">
+      <c r="C78" s="24"/>
+      <c r="D78" s="24"/>
+      <c r="E78" s="24"/>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B79" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="E79" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B78" s="12">
-        <v>1</v>
-      </c>
-      <c r="C78" s="12">
-        <v>1</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E78" s="14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B79" s="12">
-        <v>1</v>
-      </c>
-      <c r="C79" s="12">
-        <v>1</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E79" s="14" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.25">
@@ -2092,10 +2115,10 @@
         <v>1</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.25">
@@ -2106,132 +2129,132 @@
         <v>1</v>
       </c>
       <c r="D81" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E81" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B82" s="12">
+        <v>1</v>
+      </c>
+      <c r="C82" s="12">
+        <v>1</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E82" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B83" s="12">
+        <v>1</v>
+      </c>
+      <c r="C83" s="12">
+        <v>1</v>
+      </c>
+      <c r="D83" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E81" s="14" t="s">
+      <c r="E83" s="14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="85" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B85" s="5"/>
-      <c r="C85" s="7" t="s">
+    <row r="87" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B87" s="5"/>
+      <c r="C87" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D85" s="5"/>
-      <c r="E85" s="6"/>
-    </row>
-    <row r="87" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="25" t="s">
+      <c r="D87" s="5"/>
+      <c r="E87" s="6"/>
+    </row>
+    <row r="89" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B89" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C87" s="24"/>
-      <c r="D87" s="24"/>
-      <c r="E87" s="24"/>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B88" s="1" t="s">
+      <c r="C89" s="24"/>
+      <c r="D89" s="24"/>
+      <c r="E89" s="24"/>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B90" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D88" s="9" t="s">
+      <c r="D90" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="E90" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B89" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C89" s="12">
-        <v>6</v>
-      </c>
-      <c r="D89" s="15" t="s">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B91" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="12">
+        <v>6</v>
+      </c>
+      <c r="D91" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E89" s="16" t="s">
+      <c r="E91" s="16" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B90" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C90" s="17">
-        <v>6</v>
-      </c>
-      <c r="D90" s="18" t="s">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B92" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="17">
+        <v>6</v>
+      </c>
+      <c r="D92" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="E90" s="19" t="s">
+      <c r="E92" s="19" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="92" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B92" s="25" t="s">
+    <row r="94" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B94" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="C92" s="24"/>
-      <c r="D92" s="24"/>
-      <c r="E92" s="24"/>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B93" s="1" t="s">
+      <c r="C94" s="24"/>
+      <c r="D94" s="24"/>
+      <c r="E94" s="24"/>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B95" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D93" s="9" t="s">
+      <c r="D95" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="E95" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B94" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C94" s="12">
-        <v>6</v>
-      </c>
-      <c r="D94" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E94" s="16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B95" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C95" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D95" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E95" s="21" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B96" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C96" s="20" t="s">
-        <v>5</v>
+      <c r="C96" s="12">
+        <v>6</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E96" s="21" t="s">
-        <v>104</v>
+        <v>102</v>
+      </c>
+      <c r="E96" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.25">
@@ -2241,8 +2264,8 @@
       <c r="C97" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D97" s="22" t="s">
-        <v>107</v>
+      <c r="D97" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="E97" s="21" t="s">
         <v>104</v>
@@ -2256,7 +2279,7 @@
         <v>5</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E98" s="21" t="s">
         <v>104</v>
@@ -2269,8 +2292,8 @@
       <c r="C99" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D99" s="18" t="s">
-        <v>105</v>
+      <c r="D99" s="22" t="s">
+        <v>107</v>
       </c>
       <c r="E99" s="21" t="s">
         <v>104</v>
@@ -2284,7 +2307,7 @@
         <v>5</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E100" s="21" t="s">
         <v>104</v>
@@ -2298,7 +2321,7 @@
         <v>5</v>
       </c>
       <c r="D101" s="18" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E101" s="21" t="s">
         <v>104</v>
@@ -2312,7 +2335,7 @@
         <v>5</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E102" s="21" t="s">
         <v>104</v>
@@ -2325,8 +2348,8 @@
       <c r="C103" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D103" s="22" t="s">
-        <v>112</v>
+      <c r="D103" s="18" t="s">
+        <v>110</v>
       </c>
       <c r="E103" s="21" t="s">
         <v>104</v>
@@ -2340,7 +2363,7 @@
         <v>5</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E104" s="21" t="s">
         <v>104</v>
@@ -2354,7 +2377,7 @@
         <v>5</v>
       </c>
       <c r="D105" s="22" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E105" s="21" t="s">
         <v>104</v>
@@ -2368,7 +2391,7 @@
         <v>5</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E106" s="21" t="s">
         <v>104</v>
@@ -2381,8 +2404,8 @@
       <c r="C107" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D107" s="18" t="s">
-        <v>116</v>
+      <c r="D107" s="22" t="s">
+        <v>114</v>
       </c>
       <c r="E107" s="21" t="s">
         <v>104</v>
@@ -2396,7 +2419,7 @@
         <v>5</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E108" s="21" t="s">
         <v>104</v>
@@ -2410,7 +2433,7 @@
         <v>5</v>
       </c>
       <c r="D109" s="18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E109" s="21" t="s">
         <v>104</v>
@@ -2424,7 +2447,7 @@
         <v>5</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E110" s="21" t="s">
         <v>104</v>
@@ -2438,7 +2461,7 @@
         <v>5</v>
       </c>
       <c r="D111" s="18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E111" s="21" t="s">
         <v>104</v>
@@ -2452,7 +2475,7 @@
         <v>5</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E112" s="21" t="s">
         <v>104</v>
@@ -2466,7 +2489,7 @@
         <v>5</v>
       </c>
       <c r="D113" s="18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E113" s="21" t="s">
         <v>104</v>
@@ -2480,7 +2503,7 @@
         <v>5</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E114" s="21" t="s">
         <v>104</v>
@@ -2494,7 +2517,7 @@
         <v>5</v>
       </c>
       <c r="D115" s="18" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E115" s="21" t="s">
         <v>104</v>
@@ -2508,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E116" s="21" t="s">
         <v>104</v>
@@ -2522,7 +2545,7 @@
         <v>5</v>
       </c>
       <c r="D117" s="18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E117" s="21" t="s">
         <v>104</v>
@@ -2536,7 +2559,7 @@
         <v>5</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E118" s="21" t="s">
         <v>104</v>
@@ -2550,60 +2573,60 @@
         <v>5</v>
       </c>
       <c r="D119" s="18" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E119" s="21" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="121" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B121" s="25" t="s">
+    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B120" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C120" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D120" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E120" s="21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B121" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C121" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D121" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E121" s="21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="123" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B123" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="C121" s="24"/>
-      <c r="D121" s="24"/>
-      <c r="E121" s="24"/>
-    </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B122" s="1" t="s">
+      <c r="C123" s="24"/>
+      <c r="D123" s="24"/>
+      <c r="E123" s="24"/>
+    </row>
+    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B124" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D122" s="9" t="s">
+      <c r="D124" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E122" s="2" t="s">
+      <c r="E124" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B123" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C123" s="12">
-        <v>2</v>
-      </c>
-      <c r="D123" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E123" s="16" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B124" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C124" s="12">
-        <v>2</v>
-      </c>
-      <c r="D124" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="E124" s="16" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.25">
@@ -2614,7 +2637,7 @@
         <v>2</v>
       </c>
       <c r="D125" s="15" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E125" s="16" t="s">
         <v>130</v>
@@ -2627,8 +2650,8 @@
       <c r="C126" s="12">
         <v>2</v>
       </c>
-      <c r="D126" s="22" t="s">
-        <v>134</v>
+      <c r="D126" s="18" t="s">
+        <v>132</v>
       </c>
       <c r="E126" s="16" t="s">
         <v>130</v>
@@ -2642,7 +2665,7 @@
         <v>2</v>
       </c>
       <c r="D127" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E127" s="16" t="s">
         <v>130</v>
@@ -2655,8 +2678,8 @@
       <c r="C128" s="12">
         <v>2</v>
       </c>
-      <c r="D128" s="18" t="s">
-        <v>136</v>
+      <c r="D128" s="22" t="s">
+        <v>134</v>
       </c>
       <c r="E128" s="16" t="s">
         <v>130</v>
@@ -2670,7 +2693,7 @@
         <v>2</v>
       </c>
       <c r="D129" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E129" s="16" t="s">
         <v>130</v>
@@ -2683,8 +2706,8 @@
       <c r="C130" s="12">
         <v>2</v>
       </c>
-      <c r="D130" s="22" t="s">
-        <v>138</v>
+      <c r="D130" s="18" t="s">
+        <v>136</v>
       </c>
       <c r="E130" s="16" t="s">
         <v>130</v>
@@ -2698,7 +2721,7 @@
         <v>2</v>
       </c>
       <c r="D131" s="15" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E131" s="16" t="s">
         <v>130</v>
@@ -2712,7 +2735,7 @@
         <v>2</v>
       </c>
       <c r="D132" s="22" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E132" s="16" t="s">
         <v>130</v>
@@ -2726,7 +2749,7 @@
         <v>2</v>
       </c>
       <c r="D133" s="15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E133" s="16" t="s">
         <v>130</v>
@@ -2740,7 +2763,7 @@
         <v>2</v>
       </c>
       <c r="D134" s="22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E134" s="16" t="s">
         <v>130</v>
@@ -2754,7 +2777,7 @@
         <v>2</v>
       </c>
       <c r="D135" s="15" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E135" s="16" t="s">
         <v>130</v>
@@ -2767,8 +2790,8 @@
       <c r="C136" s="12">
         <v>2</v>
       </c>
-      <c r="D136" s="18" t="s">
-        <v>144</v>
+      <c r="D136" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="E136" s="16" t="s">
         <v>130</v>
@@ -2782,7 +2805,7 @@
         <v>2</v>
       </c>
       <c r="D137" s="15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E137" s="16" t="s">
         <v>130</v>
@@ -2796,7 +2819,7 @@
         <v>2</v>
       </c>
       <c r="D138" s="18" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E138" s="16" t="s">
         <v>130</v>
@@ -2810,7 +2833,7 @@
         <v>2</v>
       </c>
       <c r="D139" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E139" s="16" t="s">
         <v>130</v>
@@ -2824,7 +2847,7 @@
         <v>2</v>
       </c>
       <c r="D140" s="18" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E140" s="16" t="s">
         <v>130</v>
@@ -2838,7 +2861,7 @@
         <v>2</v>
       </c>
       <c r="D141" s="15" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E141" s="16" t="s">
         <v>130</v>
@@ -2849,10 +2872,10 @@
         <v>5</v>
       </c>
       <c r="C142" s="12">
-        <v>6</v>
-      </c>
-      <c r="D142" s="22" t="s">
-        <v>150</v>
+        <v>2</v>
+      </c>
+      <c r="D142" s="18" t="s">
+        <v>148</v>
       </c>
       <c r="E142" s="16" t="s">
         <v>130</v>
@@ -2866,7 +2889,7 @@
         <v>2</v>
       </c>
       <c r="D143" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E143" s="16" t="s">
         <v>130</v>
@@ -2877,10 +2900,10 @@
         <v>5</v>
       </c>
       <c r="C144" s="12">
-        <v>2</v>
-      </c>
-      <c r="D144" s="18" t="s">
-        <v>152</v>
+        <v>6</v>
+      </c>
+      <c r="D144" s="22" t="s">
+        <v>150</v>
       </c>
       <c r="E144" s="16" t="s">
         <v>130</v>
@@ -2891,10 +2914,10 @@
         <v>5</v>
       </c>
       <c r="C145" s="12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D145" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E145" s="16" t="s">
         <v>130</v>
@@ -2905,10 +2928,10 @@
         <v>5</v>
       </c>
       <c r="C146" s="12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D146" s="18" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E146" s="16" t="s">
         <v>130</v>
@@ -2922,7 +2945,7 @@
         <v>6</v>
       </c>
       <c r="D147" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E147" s="16" t="s">
         <v>130</v>
@@ -2935,8 +2958,8 @@
       <c r="C148" s="12">
         <v>6</v>
       </c>
-      <c r="D148" s="22" t="s">
-        <v>156</v>
+      <c r="D148" s="18" t="s">
+        <v>154</v>
       </c>
       <c r="E148" s="16" t="s">
         <v>130</v>
@@ -2947,12 +2970,40 @@
         <v>5</v>
       </c>
       <c r="C149" s="12">
+        <v>6</v>
+      </c>
+      <c r="D149" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="E149" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B150" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C150" s="12">
+        <v>6</v>
+      </c>
+      <c r="D150" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="E150" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="151" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B151" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C151" s="12">
         <v>2</v>
       </c>
-      <c r="D149" s="15" t="s">
+      <c r="D151" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="E149" s="16" t="s">
+      <c r="E151" s="16" t="s">
         <v>130</v>
       </c>
     </row>
@@ -2961,10 +3012,10 @@
     <sortCondition ref="D64:D73"/>
   </sortState>
   <mergeCells count="9">
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B123:E123"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="B15:E15"/>
